--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -879,12 +879,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -905,12 +905,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -957,12 +957,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -983,12 +983,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SDSNPLXX01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Short duration storage Nepal, region XX</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1373,23 +1373,127 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>SDSLKAXX01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Short duration storage Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OperationalLifeStorage</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>19</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>StorageLevelStart</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>19</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OperationalLifeStorage</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>SDSNPLXX01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>StorageLevelStart</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SDSNPLXX01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Short duration storage Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>OperationalLifeStorage</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G41" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1405,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -3345,12 +3449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3457,12 +3561,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3569,12 +3673,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3591,88 +3695,88 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ20" t="n">
-        <v>67291.66666666667</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="21">
@@ -3681,12 +3785,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3793,12 +3897,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3905,12 +4009,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4017,12 +4121,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4129,12 +4233,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4241,12 +4345,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4353,12 +4457,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4465,12 +4569,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4577,12 +4681,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4595,92 +4699,92 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="J29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="K29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="L29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="M29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="N29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="O29" t="n">
-        <v>9.000000000000001e-05</v>
+        <v/>
       </c>
       <c r="P29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="Q29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="R29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="S29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="T29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="U29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="V29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="W29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="X29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="Y29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="Z29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="AA29" t="n">
-        <v>0.00156</v>
+        <v/>
       </c>
       <c r="AB29" t="n">
-        <v>0.00153</v>
+        <v/>
       </c>
       <c r="AC29" t="n">
-        <v>0.00153</v>
+        <v/>
       </c>
       <c r="AD29" t="n">
-        <v>0.00153</v>
+        <v/>
       </c>
       <c r="AE29" t="n">
-        <v>0.00153</v>
+        <v/>
       </c>
       <c r="AF29" t="n">
-        <v>0.00153</v>
+        <v/>
       </c>
       <c r="AG29" t="n">
-        <v>0.00148</v>
+        <v/>
       </c>
       <c r="AH29" t="n">
-        <v>0.00148</v>
+        <v/>
       </c>
       <c r="AI29" t="n">
-        <v>0.00148</v>
+        <v/>
       </c>
       <c r="AJ29" t="n">
-        <v>0.00148</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -4689,12 +4793,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -4801,12 +4905,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4823,88 +4927,88 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="T31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="U31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="W31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="X31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.00144</v>
+        <v>0.00156</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.00144</v>
+        <v>0.00153</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.00144</v>
+        <v>0.00153</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.00144</v>
+        <v>0.00153</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.00144</v>
+        <v>0.00153</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.00144</v>
+        <v>0.00153</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.00144</v>
+        <v>0.00148</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.00144</v>
+        <v>0.00148</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.00144</v>
+        <v>0.00148</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.00144</v>
+        <v>0.00148</v>
       </c>
     </row>
     <row r="32">
@@ -4913,12 +5017,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5025,12 +5129,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5068,67 +5172,67 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00081</v>
+        <v>0.00144</v>
       </c>
     </row>
     <row r="34">
@@ -5137,12 +5241,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5249,12 +5353,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -5267,92 +5371,92 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="Q35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="R35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="S35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="T35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="U35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="V35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="W35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="X35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="Y35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="Z35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AA35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AB35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AC35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AD35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AE35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AF35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AG35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AH35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AI35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
       <c r="AJ35" t="n">
-        <v/>
+        <v>0.00081</v>
       </c>
     </row>
     <row r="36">
@@ -5361,12 +5465,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SDSNPLXX01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Short duration storage Nepal, region XX</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -5473,109 +5577,557 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>SDSLKAXX01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Short duration storage Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ResidualStorageCapacity</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v/>
+      </c>
+      <c r="J37" t="n">
+        <v/>
+      </c>
+      <c r="K37" t="n">
+        <v/>
+      </c>
+      <c r="L37" t="n">
+        <v/>
+      </c>
+      <c r="M37" t="n">
+        <v/>
+      </c>
+      <c r="N37" t="n">
+        <v/>
+      </c>
+      <c r="O37" t="n">
+        <v/>
+      </c>
+      <c r="P37" t="n">
+        <v/>
+      </c>
+      <c r="Q37" t="n">
+        <v/>
+      </c>
+      <c r="R37" t="n">
+        <v/>
+      </c>
+      <c r="S37" t="n">
+        <v/>
+      </c>
+      <c r="T37" t="n">
+        <v/>
+      </c>
+      <c r="U37" t="n">
+        <v/>
+      </c>
+      <c r="V37" t="n">
+        <v/>
+      </c>
+      <c r="W37" t="n">
+        <v/>
+      </c>
+      <c r="X37" t="n">
+        <v/>
+      </c>
+      <c r="Y37" t="n">
+        <v/>
+      </c>
+      <c r="Z37" t="n">
+        <v/>
+      </c>
+      <c r="AA37" t="n">
+        <v/>
+      </c>
+      <c r="AB37" t="n">
+        <v/>
+      </c>
+      <c r="AC37" t="n">
+        <v/>
+      </c>
+      <c r="AD37" t="n">
+        <v/>
+      </c>
+      <c r="AE37" t="n">
+        <v/>
+      </c>
+      <c r="AF37" t="n">
+        <v/>
+      </c>
+      <c r="AG37" t="n">
+        <v/>
+      </c>
+      <c r="AH37" t="n">
+        <v/>
+      </c>
+      <c r="AI37" t="n">
+        <v/>
+      </c>
+      <c r="AJ37" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>19</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>User defined</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="J38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="K38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="L38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="M38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="N38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="O38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="P38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="R38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="S38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="T38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="U38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="V38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="W38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="X38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>67291.66666666667</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>19</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ResidualStorageCapacity</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v/>
+      </c>
+      <c r="J39" t="n">
+        <v/>
+      </c>
+      <c r="K39" t="n">
+        <v/>
+      </c>
+      <c r="L39" t="n">
+        <v/>
+      </c>
+      <c r="M39" t="n">
+        <v/>
+      </c>
+      <c r="N39" t="n">
+        <v/>
+      </c>
+      <c r="O39" t="n">
+        <v/>
+      </c>
+      <c r="P39" t="n">
+        <v/>
+      </c>
+      <c r="Q39" t="n">
+        <v/>
+      </c>
+      <c r="R39" t="n">
+        <v/>
+      </c>
+      <c r="S39" t="n">
+        <v/>
+      </c>
+      <c r="T39" t="n">
+        <v/>
+      </c>
+      <c r="U39" t="n">
+        <v/>
+      </c>
+      <c r="V39" t="n">
+        <v/>
+      </c>
+      <c r="W39" t="n">
+        <v/>
+      </c>
+      <c r="X39" t="n">
+        <v/>
+      </c>
+      <c r="Y39" t="n">
+        <v/>
+      </c>
+      <c r="Z39" t="n">
+        <v/>
+      </c>
+      <c r="AA39" t="n">
+        <v/>
+      </c>
+      <c r="AB39" t="n">
+        <v/>
+      </c>
+      <c r="AC39" t="n">
+        <v/>
+      </c>
+      <c r="AD39" t="n">
+        <v/>
+      </c>
+      <c r="AE39" t="n">
+        <v/>
+      </c>
+      <c r="AF39" t="n">
+        <v/>
+      </c>
+      <c r="AG39" t="n">
+        <v/>
+      </c>
+      <c r="AH39" t="n">
+        <v/>
+      </c>
+      <c r="AI39" t="n">
+        <v/>
+      </c>
+      <c r="AJ39" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>SDSNPLXX01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CapitalCostStorage</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>User defined</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="J40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="K40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="L40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="M40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="N40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="O40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="P40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="R40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="S40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="T40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="U40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="V40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="W40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="X40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>67291.66666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SDSNPLXX01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Short duration storage Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>ResidualStorageCapacity</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v/>
-      </c>
-      <c r="J37" t="n">
-        <v/>
-      </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
-      <c r="Q37" t="n">
-        <v/>
-      </c>
-      <c r="R37" t="n">
-        <v/>
-      </c>
-      <c r="S37" t="n">
-        <v/>
-      </c>
-      <c r="T37" t="n">
-        <v/>
-      </c>
-      <c r="U37" t="n">
-        <v/>
-      </c>
-      <c r="V37" t="n">
-        <v/>
-      </c>
-      <c r="W37" t="n">
-        <v/>
-      </c>
-      <c r="X37" t="n">
-        <v/>
-      </c>
-      <c r="Y37" t="n">
-        <v/>
-      </c>
-      <c r="Z37" t="n">
-        <v/>
-      </c>
-      <c r="AA37" t="n">
-        <v/>
-      </c>
-      <c r="AB37" t="n">
-        <v/>
-      </c>
-      <c r="AC37" t="n">
-        <v/>
-      </c>
-      <c r="AD37" t="n">
-        <v/>
-      </c>
-      <c r="AE37" t="n">
-        <v/>
-      </c>
-      <c r="AF37" t="n">
-        <v/>
-      </c>
-      <c r="AG37" t="n">
-        <v/>
-      </c>
-      <c r="AH37" t="n">
-        <v/>
-      </c>
-      <c r="AI37" t="n">
-        <v/>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="I41" t="n">
+        <v/>
+      </c>
+      <c r="J41" t="n">
+        <v/>
+      </c>
+      <c r="K41" t="n">
+        <v/>
+      </c>
+      <c r="L41" t="n">
+        <v/>
+      </c>
+      <c r="M41" t="n">
+        <v/>
+      </c>
+      <c r="N41" t="n">
+        <v/>
+      </c>
+      <c r="O41" t="n">
+        <v/>
+      </c>
+      <c r="P41" t="n">
+        <v/>
+      </c>
+      <c r="Q41" t="n">
+        <v/>
+      </c>
+      <c r="R41" t="n">
+        <v/>
+      </c>
+      <c r="S41" t="n">
+        <v/>
+      </c>
+      <c r="T41" t="n">
+        <v/>
+      </c>
+      <c r="U41" t="n">
+        <v/>
+      </c>
+      <c r="V41" t="n">
+        <v/>
+      </c>
+      <c r="W41" t="n">
+        <v/>
+      </c>
+      <c r="X41" t="n">
+        <v/>
+      </c>
+      <c r="Y41" t="n">
+        <v/>
+      </c>
+      <c r="Z41" t="n">
+        <v/>
+      </c>
+      <c r="AA41" t="n">
+        <v/>
+      </c>
+      <c r="AB41" t="n">
+        <v/>
+      </c>
+      <c r="AC41" t="n">
+        <v/>
+      </c>
+      <c r="AD41" t="n">
+        <v/>
+      </c>
+      <c r="AE41" t="n">
+        <v/>
+      </c>
+      <c r="AF41" t="n">
+        <v/>
+      </c>
+      <c r="AG41" t="n">
+        <v/>
+      </c>
+      <c r="AH41" t="n">
+        <v/>
+      </c>
+      <c r="AI41" t="n">
+        <v/>
+      </c>
+      <c r="AJ41" t="n">
         <v/>
       </c>
     </row>
@@ -5591,7 +6143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6810,22 +7362,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -6846,22 +7398,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -6882,22 +7434,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -6918,22 +7470,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRLDSMDVXX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Long duration storage (Power generator) Maldives, region XX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>LDSMDVXX01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Long duration storage Maldives, region XX</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -6954,22 +7506,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -6990,22 +7542,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -7026,22 +7578,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -7062,22 +7614,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -7098,22 +7650,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -7134,22 +7686,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -7170,22 +7722,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -7206,22 +7758,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -7242,22 +7794,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -7278,22 +7830,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -7314,22 +7866,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -7350,22 +7902,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -7386,22 +7938,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -7422,22 +7974,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -7458,22 +8010,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -7494,22 +8046,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -7530,22 +8082,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -7566,22 +8118,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -7602,22 +8154,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -7638,22 +8190,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -7674,22 +8226,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -7710,22 +8262,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -7746,22 +8298,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -7782,22 +8334,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -7818,22 +8370,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -7854,22 +8406,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -7890,22 +8442,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -7926,22 +8478,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7962,22 +8514,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -7998,22 +8550,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8034,22 +8586,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -8070,22 +8622,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -8106,22 +8658,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PWRSDSNPLXX</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SDSNPLXX01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Short duration storage Nepal, region XX</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -8142,22 +8694,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PWRSDSNPLXX</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SDSNPLXX01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Short duration storage Nepal, region XX</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8178,22 +8730,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PWRSDSNPLXX</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SDSNPLXX01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Short duration storage Nepal, region XX</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8214,33 +8766,321 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>PWRSDSLKAXX</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SDSLKAXX01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Short duration storage Sri Lanka, region XX</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PWRSDSMDVXX</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SDSMDVXX01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Short duration storage Maldives, region XX</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>PWRSDSNPLXX</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>SDSNPLXX01</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PWRSDSNPLXX</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SDSNPLXX01</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Short duration storage Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>TechnologyFromStorage</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PWRSDSNPLXX</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SDSNPLXX01</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Short duration storage Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>TechnologyToStorage</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PWRSDSNPLXX</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SDSNPLXX01</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Short duration storage Nepal, region XX</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>TechnologyFromStorage</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
         <v>1</v>
       </c>
     </row>

--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -879,12 +879,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -905,12 +905,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -931,12 +931,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -957,12 +957,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -983,12 +983,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1390,110 +1390,6 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>StorageLevelStart</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OperationalLifeStorage</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>StorageLevelStart</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>OperationalLifeStorage</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1509,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ41"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -3449,12 +3345,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3561,12 +3457,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3673,12 +3569,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3695,88 +3591,88 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="J20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="L20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="M20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="O20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="P20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Q20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="R20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="S20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="T20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="U20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="V20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="W20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="X20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Y20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Z20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AA20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AB20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AC20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AD20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AE20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AF20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AG20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AH20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AI20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AJ20" t="n">
-        <v>52694.44444444445</v>
+        <v>67291.66666666667</v>
       </c>
     </row>
     <row r="21">
@@ -3785,12 +3681,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3897,12 +3793,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4009,12 +3905,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4121,12 +4017,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4233,12 +4129,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4345,12 +4241,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4457,12 +4353,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4569,12 +4465,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4681,12 +4577,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4699,92 +4595,92 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="J29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="M29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="N29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="O29" t="n">
-        <v/>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="P29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="Q29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="R29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="S29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="T29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="U29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="V29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="W29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="X29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="Y29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="Z29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="AA29" t="n">
-        <v/>
+        <v>0.00156</v>
       </c>
       <c r="AB29" t="n">
-        <v/>
+        <v>0.00153</v>
       </c>
       <c r="AC29" t="n">
-        <v/>
+        <v>0.00153</v>
       </c>
       <c r="AD29" t="n">
-        <v/>
+        <v>0.00153</v>
       </c>
       <c r="AE29" t="n">
-        <v/>
+        <v>0.00153</v>
       </c>
       <c r="AF29" t="n">
-        <v/>
+        <v>0.00153</v>
       </c>
       <c r="AG29" t="n">
-        <v/>
+        <v>0.00148</v>
       </c>
       <c r="AH29" t="n">
-        <v/>
+        <v>0.00148</v>
       </c>
       <c r="AI29" t="n">
-        <v/>
+        <v>0.00148</v>
       </c>
       <c r="AJ29" t="n">
-        <v/>
+        <v>0.00148</v>
       </c>
     </row>
     <row r="30">
@@ -4793,12 +4689,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -4905,12 +4801,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4927,88 +4823,88 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="T31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="U31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="W31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="X31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.00156</v>
+        <v>0.00144</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.00153</v>
+        <v>0.00144</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.00153</v>
+        <v>0.00144</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.00153</v>
+        <v>0.00144</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.00153</v>
+        <v>0.00144</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.00153</v>
+        <v>0.00144</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.00148</v>
+        <v>0.00144</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.00148</v>
+        <v>0.00144</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.00148</v>
+        <v>0.00144</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.00148</v>
+        <v>0.00144</v>
       </c>
     </row>
     <row r="32">
@@ -5017,12 +4913,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5129,12 +5025,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5172,67 +5068,67 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00144</v>
+        <v>0.00081</v>
       </c>
     </row>
     <row r="34">
@@ -5241,12 +5137,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5353,12 +5249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -5371,92 +5267,92 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="P35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="Q35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="R35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="S35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="T35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="U35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="V35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="W35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="X35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="Y35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="Z35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AA35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AB35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AC35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AD35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AE35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AF35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AG35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AH35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AI35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
       <c r="AJ35" t="n">
-        <v>0.00081</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -5465,12 +5361,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -5577,12 +5473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -5680,454 +5576,6 @@
         <v/>
       </c>
       <c r="AJ37" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>User defined</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="J38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="K38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="L38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="M38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="N38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="O38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="P38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="R38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="S38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="T38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="U38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="V38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="W38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="X38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>67291.66666666667</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>19</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ResidualStorageCapacity</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v/>
-      </c>
-      <c r="J39" t="n">
-        <v/>
-      </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
-      <c r="Q39" t="n">
-        <v/>
-      </c>
-      <c r="R39" t="n">
-        <v/>
-      </c>
-      <c r="S39" t="n">
-        <v/>
-      </c>
-      <c r="T39" t="n">
-        <v/>
-      </c>
-      <c r="U39" t="n">
-        <v/>
-      </c>
-      <c r="V39" t="n">
-        <v/>
-      </c>
-      <c r="W39" t="n">
-        <v/>
-      </c>
-      <c r="X39" t="n">
-        <v/>
-      </c>
-      <c r="Y39" t="n">
-        <v/>
-      </c>
-      <c r="Z39" t="n">
-        <v/>
-      </c>
-      <c r="AA39" t="n">
-        <v/>
-      </c>
-      <c r="AB39" t="n">
-        <v/>
-      </c>
-      <c r="AC39" t="n">
-        <v/>
-      </c>
-      <c r="AD39" t="n">
-        <v/>
-      </c>
-      <c r="AE39" t="n">
-        <v/>
-      </c>
-      <c r="AF39" t="n">
-        <v/>
-      </c>
-      <c r="AG39" t="n">
-        <v/>
-      </c>
-      <c r="AH39" t="n">
-        <v/>
-      </c>
-      <c r="AI39" t="n">
-        <v/>
-      </c>
-      <c r="AJ39" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>20</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>CapitalCostStorage</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>User defined</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="J40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="K40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="L40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="M40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="N40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="O40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="P40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="R40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="S40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="T40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="U40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="V40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="W40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="X40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>67291.66666666667</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>20</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ResidualStorageCapacity</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v/>
-      </c>
-      <c r="J41" t="n">
-        <v/>
-      </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
-      <c r="Q41" t="n">
-        <v/>
-      </c>
-      <c r="R41" t="n">
-        <v/>
-      </c>
-      <c r="S41" t="n">
-        <v/>
-      </c>
-      <c r="T41" t="n">
-        <v/>
-      </c>
-      <c r="U41" t="n">
-        <v/>
-      </c>
-      <c r="V41" t="n">
-        <v/>
-      </c>
-      <c r="W41" t="n">
-        <v/>
-      </c>
-      <c r="X41" t="n">
-        <v/>
-      </c>
-      <c r="Y41" t="n">
-        <v/>
-      </c>
-      <c r="Z41" t="n">
-        <v/>
-      </c>
-      <c r="AA41" t="n">
-        <v/>
-      </c>
-      <c r="AB41" t="n">
-        <v/>
-      </c>
-      <c r="AC41" t="n">
-        <v/>
-      </c>
-      <c r="AD41" t="n">
-        <v/>
-      </c>
-      <c r="AE41" t="n">
-        <v/>
-      </c>
-      <c r="AF41" t="n">
-        <v/>
-      </c>
-      <c r="AG41" t="n">
-        <v/>
-      </c>
-      <c r="AH41" t="n">
-        <v/>
-      </c>
-      <c r="AI41" t="n">
-        <v/>
-      </c>
-      <c r="AJ41" t="n">
         <v/>
       </c>
     </row>
@@ -6143,7 +5591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7362,22 +6810,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PWRLDSMDVXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Maldives, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -7398,22 +6846,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PWRLDSMDVXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Maldives, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -7434,22 +6882,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PWRLDSMDVXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Maldives, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -7470,22 +6918,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PWRLDSMDVXX</t>
+          <t>PWRLDSNPLXX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Maldives, region XX</t>
+          <t>Long duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LDSMDVXX01</t>
+          <t>LDSNPLXX01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Long duration storage Maldives, region XX</t>
+          <t>Long duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -7506,22 +6954,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -7542,22 +6990,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -7578,22 +7026,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -7614,22 +7062,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PWRLDSNPLXX</t>
+          <t>PWRSDSBGDXX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Long duration storage (Power generator) Nepal, region XX</t>
+          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LDSNPLXX01</t>
+          <t>SDSBGDXX01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Long duration storage Nepal, region XX</t>
+          <t>Short duration storage Bangladesh, region XX</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -7650,22 +7098,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -7686,22 +7134,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -7722,22 +7170,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -7758,22 +7206,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PWRSDSBGDXX</t>
+          <t>PWRSDSBTNXX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bangladesh, region XX</t>
+          <t>Short duration storage (Power generator) Bhutan, region XX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SDSBGDXX01</t>
+          <t>SDSBTNXX01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Short duration storage Bangladesh, region XX</t>
+          <t>Short duration storage Bhutan, region XX</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -7794,22 +7242,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -7830,22 +7278,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -7866,22 +7314,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -7902,22 +7350,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PWRSDSBTNXX</t>
+          <t>PWRSDSINDEA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Bhutan, region XX</t>
+          <t>Short duration storage (Power generator) India, region EA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SDSBTNXX01</t>
+          <t>SDSINDEA01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Short duration storage Bhutan, region XX</t>
+          <t>Short duration storage India, region EA</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -7938,22 +7386,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -7974,22 +7422,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -8010,22 +7458,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -8046,22 +7494,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PWRSDSINDEA</t>
+          <t>PWRSDSINDNE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region EA</t>
+          <t>Short duration storage (Power generator) India, region NE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SDSINDEA01</t>
+          <t>SDSINDNE01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Short duration storage India, region EA</t>
+          <t>Short duration storage India, region NE</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -8082,22 +7530,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -8118,22 +7566,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -8154,22 +7602,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -8190,22 +7638,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PWRSDSINDNE</t>
+          <t>PWRSDSINDNO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NE</t>
+          <t>Short duration storage (Power generator) India, region NO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SDSINDNE01</t>
+          <t>SDSINDNO01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NE</t>
+          <t>Short duration storage India, region NO</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -8226,22 +7674,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -8262,22 +7710,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -8298,22 +7746,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -8334,22 +7782,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PWRSDSINDNO</t>
+          <t>PWRSDSINDSO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region NO</t>
+          <t>Short duration storage (Power generator) India, region SO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SDSINDNO01</t>
+          <t>SDSINDSO01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Short duration storage India, region NO</t>
+          <t>Short duration storage India, region SO</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -8370,22 +7818,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -8406,22 +7854,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -8442,22 +7890,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -8478,22 +7926,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PWRSDSINDSO</t>
+          <t>PWRSDSINDWE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region SO</t>
+          <t>Short duration storage (Power generator) India, region WE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SDSINDSO01</t>
+          <t>SDSINDWE01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Short duration storage India, region SO</t>
+          <t>Short duration storage India, region WE</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -8514,22 +7962,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8550,22 +7998,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8586,22 +8034,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -8622,22 +8070,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PWRSDSINDWE</t>
+          <t>PWRSDSLKAXX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) India, region WE</t>
+          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SDSINDWE01</t>
+          <t>SDSLKAXX01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Short duration storage India, region WE</t>
+          <t>Short duration storage Sri Lanka, region XX</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -8658,22 +8106,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSNPLXX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -8694,22 +8142,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSNPLXX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -8730,22 +8178,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSNPLXX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -8766,22 +8214,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PWRSDSLKAXX</t>
+          <t>PWRSDSNPLXX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Short duration storage (Power generator) Sri Lanka, region XX</t>
+          <t>Short duration storage (Power generator) Nepal, region XX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SDSLKAXX01</t>
+          <t>SDSNPLXX01</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Short duration storage Sri Lanka, region XX</t>
+          <t>Short duration storage Nepal, region XX</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -8793,294 +8241,6 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>PWRSDSMDVXX</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>TechnologyToStorage</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>PWRSDSMDVXX</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>TechnologyFromStorage</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>2</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>PWRSDSMDVXX</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>TechnologyToStorage</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>2</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PWRSDSMDVXX</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>SDSMDVXX01</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Short duration storage Maldives, region XX</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>TechnologyFromStorage</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>1</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>PWRSDSNPLXX</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>TechnologyToStorage</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>1</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>PWRSDSNPLXX</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>TechnologyFromStorage</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PWRSDSNPLXX</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>TechnologyToStorage</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PWRSDSNPLXX</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Short duration storage (Power generator) Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>SDSNPLXX01</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Short duration storage Nepal, region XX</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>TechnologyFromStorage</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
         <v>1</v>
       </c>
     </row>

--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -2562,11 +2562,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2575,88 +2575,88 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="J10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="K10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="L10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="M10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="N10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="O10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="P10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Q10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="R10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="S10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="T10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="U10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="V10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="W10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="X10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Y10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Z10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AA10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AB10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AC10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AD10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AE10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AF10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AG10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AH10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AI10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AJ10" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11">
@@ -2674,11 +2674,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2687,88 +2687,88 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="12">
@@ -3682,101 +3682,101 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="J20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="K20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="L20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="M20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="N20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="O20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="P20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Q20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="R20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="S20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="T20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="U20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="V20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="W20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="X20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Y20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Z20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AA20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AB20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AC20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AD20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AE20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AF20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AG20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AH20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AI20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AJ20" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3794,101 +3794,101 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="J21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="K21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="L21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="M21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="N21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="O21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="P21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="R21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="S21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="T21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="U21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="V21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="W21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="X21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ21" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="22">
@@ -4802,11 +4802,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4815,88 +4815,88 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="J30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="M30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="N30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="O30" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="P30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Q30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="R30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="S30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="T30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="U30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="V30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="W30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="X30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Y30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Z30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="AA30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="AB30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AC30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AD30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AE30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AF30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AG30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AH30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AI30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AJ30" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
     </row>
     <row r="31">
@@ -4914,11 +4914,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4927,88 +4927,88 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="L31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="M31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="O31" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="T31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="U31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="V31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="W31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="X31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
     </row>
     <row r="32">

--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -2562,11 +2562,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2575,88 +2575,88 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="J10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="K10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="L10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="N10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="O10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="P10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="R10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="S10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="T10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="U10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="V10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="W10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="X10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.036</v>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="11">
@@ -2674,11 +2674,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2687,88 +2687,88 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="J11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="K11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="L11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="M11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="N11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="O11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="P11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Q11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="R11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="S11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="T11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="U11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="V11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="W11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="X11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Y11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="Z11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AA11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AB11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AC11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AD11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AE11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AF11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AG11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AH11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AI11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
       <c r="AJ11" t="n">
-        <v>52694.44444444445</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="12">
@@ -3682,101 +3682,101 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>User defined</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="J20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="K20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="L20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="M20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="N20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="O20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="P20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Q20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="R20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="S20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="T20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="U20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="V20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="W20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="X20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Y20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="Z20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AA20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AB20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AC20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AD20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AE20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AF20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AG20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AH20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AI20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
       <c r="AJ20" t="n">
-        <v/>
+        <v>52694.44444444445</v>
       </c>
     </row>
     <row r="21">
@@ -3794,101 +3794,101 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>User defined</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="J21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="K21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="L21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="M21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="N21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="O21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="P21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Q21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="R21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="S21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="T21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="U21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="V21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="W21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="X21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Y21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="Z21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AA21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AB21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AC21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AD21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AE21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AF21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AG21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AH21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AI21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
       <c r="AJ21" t="n">
-        <v>52694.44444444445</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -4802,11 +4802,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ResidualStorageCapacity</t>
+          <t>CapitalCostStorage</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4815,88 +4815,88 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="J30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="L30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="M30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="N30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="O30" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="R30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="T30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="V30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="W30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="X30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.00156</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.00153</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.00148</v>
+        <v>67291.66666666667</v>
       </c>
     </row>
     <row r="31">
@@ -4914,11 +4914,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CapitalCostStorage</t>
+          <t>ResidualStorageCapacity</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4927,88 +4927,88 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="J31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="M31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="N31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="O31" t="n">
-        <v>67291.66666666667</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="P31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Q31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="R31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="S31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="T31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="U31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="V31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="W31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="X31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Y31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="Z31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="AA31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00156</v>
       </c>
       <c r="AB31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AC31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AD31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AE31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AF31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00153</v>
       </c>
       <c r="AG31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AH31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AI31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
       <c r="AJ31" t="n">
-        <v>67291.66666666667</v>
+        <v>0.00148</v>
       </c>
     </row>
     <row r="32">

--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Storage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Horizon Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CapitalCostStorage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TechnologyStorage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fixed Horizon Parameters'!$A$1:$G$277</definedName>
